--- a/vecco_database.xlsx
+++ b/vecco_database.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insumos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recetas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Insumos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Recetas" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -8917,7 +8917,7 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
@@ -8938,7 +8938,7 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
@@ -8959,7 +8959,7 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="E545" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="546">
@@ -13957,7 +13957,7 @@
         </is>
       </c>
       <c r="E546" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="547">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="E547" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="548">
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="E548" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="549">
@@ -14020,7 +14020,7 @@
         </is>
       </c>
       <c r="E549" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="550">
@@ -14440,7 +14440,7 @@
         </is>
       </c>
       <c r="E569" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="570">
@@ -14461,7 +14461,7 @@
         </is>
       </c>
       <c r="E570" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="571">
@@ -14482,7 +14482,7 @@
         </is>
       </c>
       <c r="E571" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="572">
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="E572" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="573">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>[MESA DULCE] CHOCOTORTA</t>
+          <t>[MESA DULCE] nan</t>
         </is>
       </c>
       <c r="E600" t="n">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>[MESA DULCE] CHOCOTORTA</t>
+          <t>[MESA DULCE] nan</t>
         </is>
       </c>
       <c r="E601" t="n">
@@ -15129,7 +15129,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>[MESA DULCE] CHOCOTORTA</t>
+          <t>[MESA DULCE] nan</t>
         </is>
       </c>
       <c r="E602" t="n">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>[MESA DULCE] CHOCOTORTA</t>
+          <t>[MESA DULCE] nan</t>
         </is>
       </c>
       <c r="E603" t="n">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>[MESA DULCE] CHOCOTORTA</t>
+          <t>[MESA DULCE] nan</t>
         </is>
       </c>
       <c r="E604" t="n">
@@ -15742,7 +15742,7 @@
         </is>
       </c>
       <c r="E631" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="632">
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="E632" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="633">
@@ -15784,7 +15784,7 @@
         </is>
       </c>
       <c r="E633" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="634">
@@ -15805,7 +15805,7 @@
         </is>
       </c>
       <c r="E634" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="635">
@@ -15826,7 +15826,7 @@
         </is>
       </c>
       <c r="E635" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="636">
@@ -15847,7 +15847,7 @@
         </is>
       </c>
       <c r="E636" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="637">
@@ -15868,7 +15868,7 @@
         </is>
       </c>
       <c r="E637" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="638">
@@ -15889,7 +15889,7 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="639">
@@ -15910,7 +15910,7 @@
         </is>
       </c>
       <c r="E639" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="640">
@@ -16645,7 +16645,7 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="675">
@@ -16666,7 +16666,7 @@
         </is>
       </c>
       <c r="E675" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="676">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="E676" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="677">
@@ -16708,7 +16708,7 @@
         </is>
       </c>
       <c r="E677" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="678">
@@ -16729,7 +16729,7 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="679">
@@ -16750,7 +16750,7 @@
         </is>
       </c>
       <c r="E679" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="680">
@@ -16813,7 +16813,7 @@
         </is>
       </c>
       <c r="E682" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="683">
@@ -16834,7 +16834,7 @@
         </is>
       </c>
       <c r="E683" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="684">
@@ -16855,7 +16855,7 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
     </row>
     <row r="685">

--- a/vecco_database.xlsx
+++ b/vecco_database.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precio_Bulto</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Precio_Unit</t>
         </is>
       </c>
@@ -456,6 +466,12 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19500</v>
+      </c>
+      <c r="E2" t="n">
         <v>780</v>
       </c>
     </row>
@@ -469,6 +485,12 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>44500</v>
+      </c>
+      <c r="E3" t="n">
         <v>4450</v>
       </c>
     </row>
@@ -482,7 +504,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12800</v>
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="5">
@@ -495,6 +523,12 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24500</v>
+      </c>
+      <c r="E5" t="n">
         <v>8166.666666666667</v>
       </c>
     </row>
@@ -508,6 +542,12 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E6" t="n">
         <v>250</v>
       </c>
     </row>
@@ -521,6 +561,12 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E7" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -534,6 +580,12 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3700</v>
+      </c>
+      <c r="E8" t="n">
         <v>7400</v>
       </c>
     </row>
@@ -547,6 +599,12 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E9" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -560,6 +618,12 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E10" t="n">
         <v>8000</v>
       </c>
     </row>
@@ -573,6 +637,12 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>192</v>
+      </c>
+      <c r="E11" t="n">
         <v>192</v>
       </c>
     </row>
@@ -586,6 +656,12 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E12" t="n">
         <v>1120</v>
       </c>
     </row>
@@ -599,6 +675,12 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E13" t="n">
         <v>22000</v>
       </c>
     </row>
@@ -612,6 +694,12 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E14" t="n">
         <v>24000</v>
       </c>
     </row>
@@ -625,6 +713,12 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E15" t="n">
         <v>32000</v>
       </c>
     </row>
@@ -638,6 +732,12 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E16" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -651,6 +751,12 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E17" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -664,6 +770,12 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>500</v>
+      </c>
+      <c r="E18" t="n">
         <v>500</v>
       </c>
     </row>
@@ -676,7 +788,9 @@
           <t>YEMAS</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
         <v>138.8888888888889</v>
       </c>
     </row>
@@ -689,7 +803,9 @@
           <t>CLARAS</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
         <v>113.6363636363636</v>
       </c>
     </row>
@@ -703,6 +819,12 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E21" t="n">
         <v>1600</v>
       </c>
     </row>
@@ -716,6 +838,12 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E22" t="n">
         <v>3000</v>
       </c>
     </row>
@@ -729,6 +857,12 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>12500</v>
+      </c>
+      <c r="E23" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -742,6 +876,12 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E24" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -755,6 +895,12 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>400</v>
+      </c>
+      <c r="E25" t="n">
         <v>400</v>
       </c>
     </row>
@@ -768,6 +914,12 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E26" t="n">
         <v>6600</v>
       </c>
     </row>
@@ -781,6 +933,12 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E27" t="n">
         <v>9000</v>
       </c>
     </row>
@@ -794,6 +952,12 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>490</v>
+      </c>
+      <c r="E28" t="n">
         <v>490</v>
       </c>
     </row>
@@ -807,6 +971,12 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>26000</v>
+      </c>
+      <c r="E29" t="n">
         <v>26000</v>
       </c>
     </row>
@@ -820,6 +990,12 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E30" t="n">
         <v>1100</v>
       </c>
     </row>
@@ -833,6 +1009,12 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D31" t="n">
+        <v>113.6363636363636</v>
+      </c>
+      <c r="E31" t="n">
         <v>2840.909090909091</v>
       </c>
     </row>
@@ -846,6 +1028,12 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -859,6 +1047,12 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>80</v>
+      </c>
+      <c r="E33" t="n">
         <v>80</v>
       </c>
     </row>
@@ -872,6 +1066,12 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>80</v>
+      </c>
+      <c r="E34" t="n">
         <v>80</v>
       </c>
     </row>
@@ -885,6 +1085,12 @@
         </is>
       </c>
       <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E35" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -898,6 +1104,12 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E36" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -911,6 +1123,12 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>12</v>
+      </c>
+      <c r="D37" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E37" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -924,6 +1142,12 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E38" t="n">
         <v>32000</v>
       </c>
     </row>
@@ -937,6 +1161,12 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E39" t="n">
         <v>32000</v>
       </c>
     </row>
@@ -950,6 +1180,12 @@
         </is>
       </c>
       <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E40" t="n">
         <v>1600</v>
       </c>
     </row>
@@ -963,6 +1199,12 @@
         </is>
       </c>
       <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>15600</v>
+      </c>
+      <c r="E41" t="n">
         <v>3120</v>
       </c>
     </row>
@@ -976,6 +1218,12 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E42" t="n">
         <v>2250</v>
       </c>
     </row>
@@ -989,6 +1237,12 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E43" t="n">
         <v>2400</v>
       </c>
     </row>
@@ -1002,6 +1256,12 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E44" t="n">
         <v>16000</v>
       </c>
     </row>
@@ -1015,6 +1275,12 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E45" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -1028,6 +1294,12 @@
         </is>
       </c>
       <c r="C46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E46" t="n">
         <v>16000</v>
       </c>
     </row>
@@ -1041,6 +1313,12 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E47" t="n">
         <v>7000</v>
       </c>
     </row>
@@ -1054,6 +1332,12 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" t="n">
+        <v>37000</v>
+      </c>
+      <c r="E48" t="n">
         <v>7400</v>
       </c>
     </row>
@@ -1067,6 +1351,12 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>500</v>
+      </c>
+      <c r="E49" t="n">
         <v>500</v>
       </c>
     </row>
@@ -1080,6 +1370,12 @@
         </is>
       </c>
       <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>32000</v>
+      </c>
+      <c r="E50" t="n">
         <v>32000</v>
       </c>
     </row>
@@ -1093,6 +1389,12 @@
         </is>
       </c>
       <c r="C51" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E51" t="n">
         <v>32352.94117647059</v>
       </c>
     </row>
@@ -1106,6 +1408,12 @@
         </is>
       </c>
       <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E52" t="n">
         <v>7666.666666666667</v>
       </c>
     </row>
@@ -1119,6 +1427,12 @@
         </is>
       </c>
       <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E53" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -1132,6 +1446,12 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E54" t="n">
         <v>1200</v>
       </c>
     </row>
@@ -1145,6 +1465,12 @@
         </is>
       </c>
       <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>840</v>
+      </c>
+      <c r="E55" t="n">
         <v>840</v>
       </c>
     </row>
@@ -1158,6 +1484,12 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E56" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -1171,6 +1503,12 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>20</v>
+      </c>
+      <c r="E57" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1184,6 +1522,12 @@
         </is>
       </c>
       <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E58" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -1197,6 +1541,12 @@
         </is>
       </c>
       <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E59" t="n">
         <v>1100</v>
       </c>
     </row>
@@ -1210,6 +1560,12 @@
         </is>
       </c>
       <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E60" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -1223,7 +1579,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6857.142857142857</v>
+        <v>3.5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>27000</v>
+      </c>
+      <c r="E61" t="n">
+        <v>7714.285714285715</v>
       </c>
     </row>
     <row r="62">
@@ -1236,6 +1598,12 @@
         </is>
       </c>
       <c r="C62" t="n">
+        <v>70</v>
+      </c>
+      <c r="D62" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E62" t="n">
         <v>85.71428571428571</v>
       </c>
     </row>
@@ -1249,6 +1617,12 @@
         </is>
       </c>
       <c r="C63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E63" t="n">
         <v>2285.714285714286</v>
       </c>
     </row>
@@ -1262,6 +1636,12 @@
         </is>
       </c>
       <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E64" t="n">
         <v>8000</v>
       </c>
     </row>
@@ -1275,6 +1655,12 @@
         </is>
       </c>
       <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>180</v>
+      </c>
+      <c r="E65" t="n">
         <v>180</v>
       </c>
     </row>
@@ -1288,6 +1674,12 @@
         </is>
       </c>
       <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E66" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -1301,6 +1693,12 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="D67" t="n">
+        <v>800</v>
+      </c>
+      <c r="E67" t="n">
         <v>6779.661016949153</v>
       </c>
     </row>
@@ -1314,6 +1712,12 @@
         </is>
       </c>
       <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E68" t="n">
         <v>14000</v>
       </c>
     </row>
@@ -1327,6 +1731,12 @@
         </is>
       </c>
       <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E69" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -1340,7 +1750,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>672.6</v>
+        <v>2</v>
+      </c>
+      <c r="D70" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="71">
@@ -1353,6 +1769,12 @@
         </is>
       </c>
       <c r="C71" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D71" t="n">
+        <v>647</v>
+      </c>
+      <c r="E71" t="n">
         <v>1294</v>
       </c>
     </row>
@@ -1366,6 +1788,12 @@
         </is>
       </c>
       <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1950</v>
+      </c>
+      <c r="E72" t="n">
         <v>1950</v>
       </c>
     </row>
@@ -1379,6 +1807,12 @@
         </is>
       </c>
       <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E73" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -1392,6 +1826,12 @@
         </is>
       </c>
       <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>150</v>
+      </c>
+      <c r="E74" t="n">
         <v>150</v>
       </c>
     </row>
@@ -1405,6 +1845,12 @@
         </is>
       </c>
       <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E75" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -1418,6 +1864,12 @@
         </is>
       </c>
       <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E76" t="n">
         <v>1250</v>
       </c>
     </row>
@@ -1431,6 +1883,12 @@
         </is>
       </c>
       <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E77" t="n">
         <v>1100</v>
       </c>
     </row>
@@ -1444,6 +1902,12 @@
         </is>
       </c>
       <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>25</v>
+      </c>
+      <c r="E78" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1457,6 +1921,12 @@
         </is>
       </c>
       <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>200</v>
+      </c>
+      <c r="E79" t="n">
         <v>200</v>
       </c>
     </row>
@@ -1470,6 +1940,12 @@
         </is>
       </c>
       <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>800</v>
+      </c>
+      <c r="E80" t="n">
         <v>800</v>
       </c>
     </row>
@@ -1483,6 +1959,12 @@
         </is>
       </c>
       <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E81" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -1496,6 +1978,12 @@
         </is>
       </c>
       <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E82" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -1509,6 +1997,12 @@
         </is>
       </c>
       <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E83" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -1522,6 +2016,12 @@
         </is>
       </c>
       <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>500</v>
+      </c>
+      <c r="E84" t="n">
         <v>500</v>
       </c>
     </row>
@@ -1535,6 +2035,12 @@
         </is>
       </c>
       <c r="C85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D85" t="n">
+        <v>19500</v>
+      </c>
+      <c r="E85" t="n">
         <v>780</v>
       </c>
     </row>
@@ -1548,7 +2054,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10000</v>
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E86" t="n">
+        <v>13000</v>
       </c>
     </row>
     <row r="87">
@@ -1561,6 +2073,12 @@
         </is>
       </c>
       <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>700</v>
+      </c>
+      <c r="E87" t="n">
         <v>700</v>
       </c>
     </row>
@@ -1574,6 +2092,12 @@
         </is>
       </c>
       <c r="C88" t="n">
+        <v>30</v>
+      </c>
+      <c r="D88" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E88" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1587,6 +2111,12 @@
         </is>
       </c>
       <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E89" t="n">
         <v>1200</v>
       </c>
     </row>
@@ -1600,6 +2130,12 @@
         </is>
       </c>
       <c r="C90" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E90" t="n">
         <v>48000</v>
       </c>
     </row>
@@ -1613,6 +2149,12 @@
         </is>
       </c>
       <c r="C91" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E91" t="n">
         <v>3000</v>
       </c>
     </row>
@@ -1626,6 +2168,12 @@
         </is>
       </c>
       <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E92" t="n">
         <v>25000</v>
       </c>
     </row>
@@ -1639,6 +2187,12 @@
         </is>
       </c>
       <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E93" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -1652,6 +2206,12 @@
         </is>
       </c>
       <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E94" t="n">
         <v>1300</v>
       </c>
     </row>
@@ -1665,6 +2225,12 @@
         </is>
       </c>
       <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>7150</v>
+      </c>
+      <c r="E95" t="n">
         <v>7150</v>
       </c>
     </row>
@@ -1678,6 +2244,12 @@
         </is>
       </c>
       <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>6300</v>
+      </c>
+      <c r="E96" t="n">
         <v>6300</v>
       </c>
     </row>
@@ -1691,6 +2263,12 @@
         </is>
       </c>
       <c r="C97" t="n">
+        <v>6</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E97" t="n">
         <v>194.1666666666667</v>
       </c>
     </row>
@@ -1704,6 +2282,12 @@
         </is>
       </c>
       <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E98" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -1717,6 +2301,12 @@
         </is>
       </c>
       <c r="C99" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D99" t="n">
+        <v>12400</v>
+      </c>
+      <c r="E99" t="n">
         <v>4275.862068965517</v>
       </c>
     </row>
@@ -1730,6 +2320,12 @@
         </is>
       </c>
       <c r="C100" t="n">
+        <v>12</v>
+      </c>
+      <c r="D100" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E100" t="n">
         <v>500</v>
       </c>
     </row>
@@ -1743,6 +2339,12 @@
         </is>
       </c>
       <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E101" t="n">
         <v>1600</v>
       </c>
     </row>
@@ -1756,6 +2358,12 @@
         </is>
       </c>
       <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>500</v>
+      </c>
+      <c r="E102" t="n">
         <v>500</v>
       </c>
     </row>
@@ -1769,6 +2377,12 @@
         </is>
       </c>
       <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E103" t="n">
         <v>2500</v>
       </c>
     </row>
@@ -1782,6 +2396,12 @@
         </is>
       </c>
       <c r="C104" t="n">
+        <v>25</v>
+      </c>
+      <c r="D104" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E104" t="n">
         <v>1120</v>
       </c>
     </row>
@@ -1795,6 +2415,12 @@
         </is>
       </c>
       <c r="C105" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D105" t="n">
+        <v>200</v>
+      </c>
+      <c r="E105" t="n">
         <v>266.6666666666667</v>
       </c>
     </row>
@@ -1808,6 +2434,12 @@
         </is>
       </c>
       <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E106" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -1821,6 +2453,12 @@
         </is>
       </c>
       <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E107" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -1834,6 +2472,12 @@
         </is>
       </c>
       <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="n">
+        <v>24500</v>
+      </c>
+      <c r="E108" t="n">
         <v>8166.666666666667</v>
       </c>
     </row>
@@ -1847,6 +2491,12 @@
         </is>
       </c>
       <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E109" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1860,6 +2510,12 @@
         </is>
       </c>
       <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E110" t="n">
         <v>3000</v>
       </c>
     </row>
@@ -1873,6 +2529,12 @@
         </is>
       </c>
       <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E111" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -1886,6 +2548,12 @@
         </is>
       </c>
       <c r="C112" t="n">
+        <v>5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E112" t="n">
         <v>6600</v>
       </c>
     </row>
@@ -1899,6 +2567,12 @@
         </is>
       </c>
       <c r="C113" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D113" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E113" t="n">
         <v>8666.666666666666</v>
       </c>
     </row>
@@ -1912,6 +2586,12 @@
         </is>
       </c>
       <c r="C114" t="n">
+        <v>7</v>
+      </c>
+      <c r="D114" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E114" t="n">
         <v>8571.428571428571</v>
       </c>
     </row>
@@ -1925,6 +2605,12 @@
         </is>
       </c>
       <c r="C115" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D115" t="n">
+        <v>13000</v>
+      </c>
+      <c r="E115" t="n">
         <v>5200</v>
       </c>
     </row>
@@ -1938,6 +2624,12 @@
         </is>
       </c>
       <c r="C116" t="n">
+        <v>18</v>
+      </c>
+      <c r="D116" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E116" t="n">
         <v>833.3333333333334</v>
       </c>
     </row>
@@ -1951,6 +2643,12 @@
         </is>
       </c>
       <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E117" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -1964,6 +2662,12 @@
         </is>
       </c>
       <c r="C118" t="n">
+        <v>12</v>
+      </c>
+      <c r="D118" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E118" t="n">
         <v>500</v>
       </c>
     </row>
@@ -1977,6 +2681,12 @@
         </is>
       </c>
       <c r="C119" t="n">
+        <v>5</v>
+      </c>
+      <c r="D119" t="n">
+        <v>17500</v>
+      </c>
+      <c r="E119" t="n">
         <v>3500</v>
       </c>
     </row>
@@ -1990,6 +2700,12 @@
         </is>
       </c>
       <c r="C120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D120" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E120" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2003,6 +2719,12 @@
         </is>
       </c>
       <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E121" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2016,6 +2738,12 @@
         </is>
       </c>
       <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E122" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -2029,6 +2757,12 @@
         </is>
       </c>
       <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E123" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -2042,6 +2776,12 @@
         </is>
       </c>
       <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>50</v>
+      </c>
+      <c r="E124" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2055,6 +2795,12 @@
         </is>
       </c>
       <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>30</v>
+      </c>
+      <c r="E125" t="n">
         <v>30</v>
       </c>
     </row>
@@ -2068,6 +2814,12 @@
         </is>
       </c>
       <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E126" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -2081,6 +2833,12 @@
         </is>
       </c>
       <c r="C127" t="n">
+        <v>12</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E127" t="n">
         <v>333.3333333333333</v>
       </c>
     </row>
@@ -2094,6 +2852,12 @@
         </is>
       </c>
       <c r="C128" t="n">
+        <v>6</v>
+      </c>
+      <c r="D128" t="n">
+        <v>350</v>
+      </c>
+      <c r="E128" t="n">
         <v>58.33333333333334</v>
       </c>
     </row>
@@ -2107,6 +2871,12 @@
         </is>
       </c>
       <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>10</v>
+      </c>
+      <c r="E129" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2120,6 +2890,12 @@
         </is>
       </c>
       <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E130" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2133,6 +2909,12 @@
         </is>
       </c>
       <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E131" t="n">
         <v>23000</v>
       </c>
     </row>
@@ -2146,6 +2928,12 @@
         </is>
       </c>
       <c r="C132" t="n">
+        <v>12</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E132" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2159,6 +2947,12 @@
         </is>
       </c>
       <c r="C133" t="n">
+        <v>5</v>
+      </c>
+      <c r="D133" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E133" t="n">
         <v>3000</v>
       </c>
     </row>
@@ -2172,6 +2966,12 @@
         </is>
       </c>
       <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>9900</v>
+      </c>
+      <c r="E134" t="n">
         <v>9900</v>
       </c>
     </row>
@@ -2185,6 +2985,12 @@
         </is>
       </c>
       <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E135" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -2198,6 +3004,12 @@
         </is>
       </c>
       <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E136" t="n">
         <v>7000</v>
       </c>
     </row>
@@ -2211,6 +3023,12 @@
         </is>
       </c>
       <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E137" t="n">
         <v>3500</v>
       </c>
     </row>
@@ -2224,6 +3042,12 @@
         </is>
       </c>
       <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>22000</v>
+      </c>
+      <c r="E138" t="n">
         <v>22000</v>
       </c>
     </row>
@@ -2237,6 +3061,12 @@
         </is>
       </c>
       <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E139" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2250,6 +3080,12 @@
         </is>
       </c>
       <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>13200</v>
+      </c>
+      <c r="E140" t="n">
         <v>13200</v>
       </c>
     </row>
@@ -2263,6 +3099,12 @@
         </is>
       </c>
       <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>170</v>
+      </c>
+      <c r="E141" t="n">
         <v>170</v>
       </c>
     </row>
@@ -2276,6 +3118,12 @@
         </is>
       </c>
       <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E142" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -2289,6 +3137,12 @@
         </is>
       </c>
       <c r="C143" t="n">
+        <v>12</v>
+      </c>
+      <c r="D143" t="n">
+        <v>700</v>
+      </c>
+      <c r="E143" t="n">
         <v>58.33333333333334</v>
       </c>
     </row>
@@ -2302,6 +3156,12 @@
         </is>
       </c>
       <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E144" t="n">
         <v>3000</v>
       </c>
     </row>
@@ -2315,6 +3175,12 @@
         </is>
       </c>
       <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>5200</v>
+      </c>
+      <c r="E145" t="n">
         <v>5200</v>
       </c>
     </row>
@@ -2328,6 +3194,12 @@
         </is>
       </c>
       <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E146" t="n">
         <v>4000</v>
       </c>
     </row>
@@ -2341,6 +3213,12 @@
         </is>
       </c>
       <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E147" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -2354,6 +3232,12 @@
         </is>
       </c>
       <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E148" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -2367,6 +3251,12 @@
         </is>
       </c>
       <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E149" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -2380,6 +3270,12 @@
         </is>
       </c>
       <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>12500</v>
+      </c>
+      <c r="E150" t="n">
         <v>12500</v>
       </c>
     </row>
@@ -2393,6 +3289,12 @@
         </is>
       </c>
       <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E151" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -2406,6 +3308,10 @@
         </is>
       </c>
       <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,6 +3325,12 @@
         </is>
       </c>
       <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>5500</v>
+      </c>
+      <c r="E153" t="n">
         <v>5500</v>
       </c>
     </row>
@@ -2432,6 +3344,12 @@
         </is>
       </c>
       <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>7900</v>
+      </c>
+      <c r="E154" t="n">
         <v>7900</v>
       </c>
     </row>
@@ -2445,6 +3363,12 @@
         </is>
       </c>
       <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E155" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -2458,6 +3382,12 @@
         </is>
       </c>
       <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>250</v>
+      </c>
+      <c r="E156" t="n">
         <v>250</v>
       </c>
     </row>
@@ -2471,6 +3401,12 @@
         </is>
       </c>
       <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>240</v>
+      </c>
+      <c r="E157" t="n">
         <v>240</v>
       </c>
     </row>

--- a/vecco_database.xlsx
+++ b/vecco_database.xlsx
@@ -15536,7 +15536,7 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>

--- a/vecco_database.xlsx
+++ b/vecco_database.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,27 +418,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Insumo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Precio_Bulto</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Precio_Unit</t>
         </is>
@@ -469,10 +457,10 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>19500</v>
+        <v>20700</v>
       </c>
       <c r="E2" t="n">
-        <v>780</v>
+        <v>828</v>
       </c>
     </row>
     <row r="3">
@@ -488,10 +476,10 @@
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>44500</v>
+        <v>60460</v>
       </c>
       <c r="E3" t="n">
-        <v>4450</v>
+        <v>6046</v>
       </c>
     </row>
     <row r="4">
@@ -504,13 +492,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>12000</v>
+        <v>53000</v>
       </c>
       <c r="E4" t="n">
-        <v>12000</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="5">
@@ -659,10 +647,10 @@
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>28000</v>
+        <v>33300</v>
       </c>
       <c r="E12" t="n">
-        <v>1120</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="13">
@@ -2038,10 +2026,10 @@
         <v>25</v>
       </c>
       <c r="D85" t="n">
-        <v>19500</v>
+        <v>20700</v>
       </c>
       <c r="E85" t="n">
-        <v>780</v>
+        <v>828</v>
       </c>
     </row>
     <row r="86">
@@ -2399,10 +2387,10 @@
         <v>25</v>
       </c>
       <c r="D104" t="n">
-        <v>28000</v>
+        <v>33300</v>
       </c>
       <c r="E104" t="n">
-        <v>1120</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="105">
@@ -3425,27 +3413,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID_Insumo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Insumo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Receta</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Porciones</t>
         </is>

--- a/vecco_database.xlsx
+++ b/vecco_database.xlsx
@@ -514,10 +514,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>24500</v>
+        <v>27000</v>
       </c>
       <c r="E5" t="n">
-        <v>8166.666666666667</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="6">
@@ -2463,10 +2463,10 @@
         <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>24500</v>
+        <v>27000</v>
       </c>
       <c r="E108" t="n">
-        <v>8166.666666666667</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="109">
